--- a/rl2.xlsx
+++ b/rl2.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="Лист 1" sheetId="19" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" calcMode="autoNoTable" iterateCount="1000" iterateDelta="9.9999999999999995E-8"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -84,9 +84,6 @@
     <t>transpor + truckNumber</t>
   </si>
   <si>
-    <t>transportCompany</t>
-  </si>
-  <si>
     <t>MR №</t>
   </si>
   <si>
@@ -103,6 +100,9 @@
   </si>
   <si>
     <t>specialist</t>
+  </si>
+  <si>
+    <t>Общество с ограниченной ответственностью "УСПЕХ", 121596, Москва г, Горбунова ул, дом № 2, строение 3, помещение II, комната 12</t>
   </si>
 </sst>
 </file>
@@ -112,7 +112,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yy;@"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -173,6 +173,14 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -539,10 +547,29 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -550,43 +577,24 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -898,16 +906,16 @@
       </c>
     </row>
     <row r="2" spans="1:13" s="3" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
+      <c r="A2" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
@@ -923,75 +931,75 @@
       <c r="H3" s="36"/>
     </row>
     <row r="4" spans="1:13" s="5" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="39" t="s">
+      <c r="A4" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="40" t="s">
+      <c r="B4" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="41"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="42"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="42"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="39"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="39"/>
     </row>
     <row r="5" spans="1:13" s="5" customFormat="1" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="39"/>
-      <c r="B5" s="42"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="42"/>
+      <c r="A5" s="38"/>
+      <c r="B5" s="39"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="39"/>
     </row>
     <row r="6" spans="1:13" s="5" customFormat="1" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="39" t="s">
+      <c r="A6" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="52" t="s">
+      <c r="B6" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="53"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="45" t="s">
+      <c r="C6" s="50"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="46"/>
-      <c r="G6" s="47" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" s="48"/>
+      <c r="F6" s="52"/>
+      <c r="G6" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="54"/>
       <c r="M6" s="1"/>
     </row>
     <row r="7" spans="1:13" s="5" customFormat="1" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="39"/>
-      <c r="B7" s="42"/>
-      <c r="C7" s="42"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="42"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="42"/>
+      <c r="A7" s="38"/>
+      <c r="B7" s="39"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="39"/>
+      <c r="F7" s="39"/>
+      <c r="G7" s="39"/>
+      <c r="H7" s="39"/>
     </row>
     <row r="8" spans="1:13" s="5" customFormat="1" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="39" t="s">
+      <c r="A8" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="49" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="50"/>
-      <c r="D8" s="50"/>
-      <c r="E8" s="50"/>
-      <c r="F8" s="50"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="42"/>
+      <c r="B8" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="44"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="39"/>
     </row>
     <row r="9" spans="1:13" s="3" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="1:13" s="3" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="54" t="s">
+      <c r="A10" s="42" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="6" t="s">
@@ -1034,10 +1042,10 @@
       <c r="E12" s="23"/>
       <c r="F12" s="24"/>
       <c r="G12" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" s="26" t="s">
         <v>26</v>
-      </c>
-      <c r="H12" s="26" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:13" s="3" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1050,7 +1058,7 @@
       <c r="C13" s="25"/>
       <c r="D13" s="28"/>
       <c r="E13" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F13" s="14"/>
       <c r="G13" s="25"/>
@@ -1067,7 +1075,7 @@
       <c r="C14" s="25"/>
       <c r="D14" s="28"/>
       <c r="E14" s="15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F14" s="14"/>
       <c r="G14" s="25"/>
@@ -1084,7 +1092,7 @@
       <c r="C15" s="30"/>
       <c r="D15" s="31"/>
       <c r="E15" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F15" s="17"/>
       <c r="G15" s="32"/>
@@ -1101,7 +1109,7 @@
       <c r="C16" s="30"/>
       <c r="D16" s="31"/>
       <c r="E16" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F16" s="17"/>
       <c r="G16" s="32"/>
@@ -1118,7 +1126,7 @@
       <c r="C17" s="30"/>
       <c r="D17" s="31"/>
       <c r="E17" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F17" s="17"/>
       <c r="G17" s="32"/>
@@ -1135,7 +1143,7 @@
       <c r="C18" s="30"/>
       <c r="D18" s="31"/>
       <c r="E18" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F18" s="17"/>
       <c r="G18" s="32"/>
@@ -1152,7 +1160,7 @@
       <c r="C19" s="31"/>
       <c r="D19" s="31"/>
       <c r="E19" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F19" s="19"/>
       <c r="G19" s="22"/>
@@ -1161,7 +1169,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B20" s="34"/>
       <c r="C20" s="34"/>

--- a/rl2.xlsx
+++ b/rl2.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="Лист 1" sheetId="19" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913" calcMode="autoNoTable" iterateCount="1000" iterateDelta="9.9999999999999995E-8"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="28">
   <si>
     <t>АО "СТОКМАНН"</t>
   </si>
@@ -878,7 +878,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -1140,44 +1140,27 @@
       <c r="B18" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="30"/>
+      <c r="C18" s="31"/>
       <c r="D18" s="31"/>
-      <c r="E18" s="16" t="s">
+      <c r="E18" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="F18" s="17"/>
-      <c r="G18" s="32"/>
-      <c r="H18" s="33"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="22"/>
       <c r="I18" s="2"/>
     </row>
-    <row r="19" spans="1:9" s="3" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="C19" s="31"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F19" s="19"/>
-      <c r="G19" s="22"/>
-      <c r="H19" s="22"/>
-      <c r="I19" s="2"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="20" t="s">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="34"/>
-      <c r="C20" s="34"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="34"/>
-      <c r="H20" s="34"/>
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="6">
